--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.20.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.20.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.20.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.20.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.20.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.20.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0020.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0020.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -606,11 +606,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]T</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]T</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L19: isolated marker/symbol line :: 13</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L3: isolated marker/symbol line :: 13</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]T</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +685,7 @@
       <c r="N3" s="1" t="inlineStr"/>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 1</t>
+          <t>L3: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -724,7 +728,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: sections it has been thought advisable to give in full :â€” Notice.</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -732,7 +736,7 @@
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: R:</t>
+          <t>L5: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -775,7 +779,7 @@
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L56: isolated marker/symbol line :: R:</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -818,7 +822,7 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -861,7 +865,7 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: N</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -904,7 +908,7 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line | line starts with punctuation glued to text :: *4</t>
+          <t>L84: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -945,7 +949,11 @@
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>L100: isolated marker/symbol line | line starts with punctuation glued to text :: *4</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1009,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1048,7 +1056,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
